--- a/ontology_release/output/evaluation/focused_comparator_matrix.xlsx
+++ b/ontology_release/output/evaluation/focused_comparator_matrix.xlsx
@@ -1663,12 +1663,12 @@
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="55" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="51" customWidth="1" min="4" max="4"/>
+    <col width="38" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
     <col width="50" customWidth="1" min="6" max="6"/>
     <col width="55" customWidth="1" min="7" max="7"/>
     <col width="42" customWidth="1" min="8" max="8"/>
-    <col width="51" customWidth="1" min="9" max="9"/>
+    <col width="38" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="14" customWidth="1" min="11" max="11"/>
     <col width="14" customWidth="1" min="12" max="12"/>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>odk/src/ontology/mirror/emmo-electrochemistry.owl</t>
+          <t>input/comparators/edo-0.39.0.owl</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>odk/src/ontology/mirror/emmo-electrochemistry.owl</t>
+          <t>input/comparators/edo-0.39.0.owl</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -1874,7 +1874,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>odk/src/ontology/mirror/hdo.owl</t>
+          <t>input/comparators/hdo-2026-09-25.owl</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -1899,7 +1899,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>odk/src/ontology/mirror/hdo.owl</t>
+          <t>input/comparators/hdo-2026-09-25.owl</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">

--- a/ontology_release/output/evaluation/focused_comparator_matrix.xlsx
+++ b/ontology_release/output/evaluation/focused_comparator_matrix.xlsx
@@ -11,7 +11,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Frozen resources" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparator matrix'!$A$1:$K$21</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Comparator matrix'!$A$1:$M$21</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Frozen resources'!$A$1:$L$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K21"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -446,6 +446,8 @@
     <col width="55" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
     <col width="55" customWidth="1" min="11" max="11"/>
+    <col width="36" customWidth="1" min="12" max="12"/>
+    <col width="42" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -491,7 +493,7 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>query_evidence</t>
+          <t>iri_presence_evidence</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
@@ -502,6 +504,16 @@
       <c r="K1" s="1" t="inlineStr">
         <is>
           <t>source_sha256</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>assessment_origin</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>automated_verification</t>
         </is>
       </c>
     </row>
@@ -558,7 +570,17 @@
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>946C462EEABDC14ECF82325AA468A40B1881C119451DB6953322F78BD96128A1</t>
+          <t>A0D6276812659804DBAB1AD009CF1A5D08C71397D402C7F0A41B11C7007421C9</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
         </is>
       </c>
     </row>
@@ -615,7 +637,17 @@
       </c>
       <c r="K3" s="2" t="inlineStr">
         <is>
-          <t>946C462EEABDC14ECF82325AA468A40B1881C119451DB6953322F78BD96128A1</t>
+          <t>A0D6276812659804DBAB1AD009CF1A5D08C71397D402C7F0A41B11C7007421C9</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
         </is>
       </c>
     </row>
@@ -672,7 +704,17 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>946C462EEABDC14ECF82325AA468A40B1881C119451DB6953322F78BD96128A1</t>
+          <t>A0D6276812659804DBAB1AD009CF1A5D08C71397D402C7F0A41B11C7007421C9</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
         </is>
       </c>
     </row>
@@ -729,7 +771,17 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>946C462EEABDC14ECF82325AA468A40B1881C119451DB6953322F78BD96128A1</t>
+          <t>A0D6276812659804DBAB1AD009CF1A5D08C71397D402C7F0A41B11C7007421C9</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
         </is>
       </c>
     </row>
@@ -786,7 +838,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>946C462EEABDC14ECF82325AA468A40B1881C119451DB6953322F78BD96128A1</t>
+          <t>A0D6276812659804DBAB1AD009CF1A5D08C71397D402C7F0A41B11C7007421C9</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
         </is>
       </c>
     </row>
@@ -846,6 +908,16 @@
           <t>78E58F277B707F271DB91BA119286F66D555B2CAA62AB046E876082F4557C2A7</t>
         </is>
       </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -903,6 +975,16 @@
           <t>78E58F277B707F271DB91BA119286F66D555B2CAA62AB046E876082F4557C2A7</t>
         </is>
       </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -960,6 +1042,16 @@
           <t>78E58F277B707F271DB91BA119286F66D555B2CAA62AB046E876082F4557C2A7</t>
         </is>
       </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1017,6 +1109,16 @@
           <t>78E58F277B707F271DB91BA119286F66D555B2CAA62AB046E876082F4557C2A7</t>
         </is>
       </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1074,6 +1176,16 @@
           <t>78E58F277B707F271DB91BA119286F66D555B2CAA62AB046E876082F4557C2A7</t>
         </is>
       </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1131,6 +1243,16 @@
           <t>6517B7B030D7DDF427977CD22F7FC31BFBE0C4107B21D6053BE4E2C4F36D0986</t>
         </is>
       </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1188,6 +1310,16 @@
           <t>6517B7B030D7DDF427977CD22F7FC31BFBE0C4107B21D6053BE4E2C4F36D0986</t>
         </is>
       </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -1245,6 +1377,16 @@
           <t>6517B7B030D7DDF427977CD22F7FC31BFBE0C4107B21D6053BE4E2C4F36D0986</t>
         </is>
       </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -1302,6 +1444,16 @@
           <t>6517B7B030D7DDF427977CD22F7FC31BFBE0C4107B21D6053BE4E2C4F36D0986</t>
         </is>
       </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -1359,6 +1511,16 @@
           <t>6517B7B030D7DDF427977CD22F7FC31BFBE0C4107B21D6053BE4E2C4F36D0986</t>
         </is>
       </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -1416,6 +1578,16 @@
           <t>6A3CD2D4604D1436E95A2A93299CE8F694F07E2EFB7B2A514265FFC416764D7B</t>
         </is>
       </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -1473,6 +1645,16 @@
           <t>6A3CD2D4604D1436E95A2A93299CE8F694F07E2EFB7B2A514265FFC416764D7B</t>
         </is>
       </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -1530,6 +1712,16 @@
           <t>6A3CD2D4604D1436E95A2A93299CE8F694F07E2EFB7B2A514265FFC416764D7B</t>
         </is>
       </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1587,6 +1779,16 @@
           <t>6A3CD2D4604D1436E95A2A93299CE8F694F07E2EFB7B2A514265FFC416764D7B</t>
         </is>
       </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1644,9 +1846,19 @@
           <t>6A3CD2D4604D1436E95A2A93299CE8F694F07E2EFB7B2A514265FFC416764D7B</t>
         </is>
       </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>author_curated_capability_judgment</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>rdf_parse_and_evidence_iri_presence_only</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K21"/>
+  <autoFilter ref="A1:M21"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1784,11 +1996,11 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>946C462EEABDC14ECF82325AA468A40B1881C119451DB6953322F78BD96128A1</t>
+          <t>A0D6276812659804DBAB1AD009CF1A5D08C71397D402C7F0A41B11C7007421C9</t>
         </is>
       </c>
       <c r="K2" s="2" t="n">
-        <v>78511</v>
+        <v>78619</v>
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
